--- a/UTCUTS/_CALIBRATION_REVIEW.xlsx
+++ b/UTCUTS/_CALIBRATION_REVIEW.xlsx
@@ -38544,7 +38544,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14A54C85-F22C-4BAD-852E-249A5842345D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{124953DC-7C1F-4752-9800-CCA34E2DF0DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
